--- a/data/trans_orig/DCD_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/DCD_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) en 2023</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35761</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72660</t>
+          <t>72502</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38377</t>
+          <t>41304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79656</t>
+          <t>82452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>379724</t>
+          <t>380487</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398008</t>
+          <t>397995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240540</t>
+          <t>240698</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277439</t>
+          <t>278048</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>633531</t>
+          <t>630735</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>674810</t>
+          <t>671883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>14672</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37374</t>
+          <t>37467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>42076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86898</t>
+          <t>88033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62387</t>
+          <t>66504</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112332</t>
+          <t>114298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386173</t>
+          <t>386080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>409471</t>
+          <t>408875</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>425195</t>
+          <t>424060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>473632</t>
+          <t>470017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>823308</t>
+          <t>821342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>873253</t>
+          <t>869136</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37112</t>
+          <t>36213</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65839</t>
+          <t>64313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73464</t>
+          <t>72376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114668</t>
+          <t>115423</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121810</t>
+          <t>122917</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168637</t>
+          <t>168447</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>470499</t>
+          <t>472025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>499226</t>
+          <t>500125</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>477334</t>
+          <t>476579</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>518538</t>
+          <t>519626</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>959703</t>
+          <t>959893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1006530</t>
+          <t>1005423</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42181</t>
+          <t>44387</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>143466</t>
+          <t>144973</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145546</t>
+          <t>148112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>194413</t>
+          <t>195902</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>158898</t>
+          <t>171288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>329935</t>
+          <t>334652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>744320</t>
+          <t>742813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>845605</t>
+          <t>843399</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>518468</t>
+          <t>516979</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>567335</t>
+          <t>564769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1270732</t>
+          <t>1266015</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1441769</t>
+          <t>1429379</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99080</t>
+          <t>99651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133825</t>
+          <t>136002</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>165480</t>
+          <t>165245</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197481</t>
+          <t>198252</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>275784</t>
+          <t>274485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>323771</t>
+          <t>324144</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>427409</t>
+          <t>425232</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462154</t>
+          <t>461583</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>350424</t>
+          <t>349653</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>382425</t>
+          <t>382660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>785368</t>
+          <t>784995</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>833355</t>
+          <t>834654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64052</t>
+          <t>65023</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87195</t>
+          <t>88362</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56879</t>
+          <t>62311</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>222283</t>
+          <t>222748</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>121455</t>
+          <t>117425</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>286451</t>
+          <t>286226</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280970</t>
+          <t>279803</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>303142</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>386085</t>
+          <t>385620</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>551489</t>
+          <t>546057</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>690082</t>
+          <t>690307</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>855078</t>
+          <t>859108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>82073</t>
+          <t>80879</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105023</t>
+          <t>105210</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>221690</t>
+          <t>219724</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>251253</t>
+          <t>251309</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>309738</t>
+          <t>309740</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>350511</t>
+          <t>347941</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177736</t>
+          <t>177549</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200686</t>
+          <t>201880</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>174578</t>
+          <t>174522</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>204141</t>
+          <t>206107</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>358079</t>
+          <t>360649</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>398852</t>
+          <t>398850</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>360611</t>
+          <t>364903</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>516813</t>
+          <t>519297</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>772295</t>
+          <t>764091</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1028292</t>
+          <t>1028185</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1227473</t>
+          <t>1213709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1521176</t>
+          <t>1516243</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2943004</t>
+          <t>2940520</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3099206</t>
+          <t>3094914</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2683988</t>
+          <t>2684095</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2939985</t>
+          <t>2948189</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5650921</t>
+          <t>5655854</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5944624</t>
+          <t>5958388</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DCD_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/DCD_R-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19500</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50324</t>
+          <t>60871</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35152</t>
+          <t>42431</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72502</t>
+          <t>82765</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>67799</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41304</t>
+          <t>47688</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82452</t>
+          <t>95229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>392781</t>
+          <t>400865</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>380487</t>
+          <t>388680</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397995</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>262876</t>
+          <t>301641</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240698</t>
+          <t>279747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>278048</t>
+          <t>320081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>655656</t>
+          <t>702506</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>630735</t>
+          <t>675076</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>671883</t>
+          <t>722617</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37467</t>
+          <t>42237</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66502</t>
+          <t>71381</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42076</t>
+          <t>54825</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88033</t>
+          <t>88327</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>89322</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66504</t>
+          <t>76824</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114298</t>
+          <t>119112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>400727</t>
+          <t>450715</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386080</t>
+          <t>434653</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408875</t>
+          <t>461355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>445591</t>
+          <t>430352</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>424060</t>
+          <t>413406</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470017</t>
+          <t>446908</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>846318</t>
+          <t>881067</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>821342</t>
+          <t>859511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>869136</t>
+          <t>901799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48943</t>
+          <t>52228</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36213</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64313</t>
+          <t>67240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>97317</t>
+          <t>113298</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72376</t>
+          <t>99114</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115423</t>
+          <t>132807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>146260</t>
+          <t>165525</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122917</t>
+          <t>145937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168447</t>
+          <t>190169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>487395</t>
+          <t>568609</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472025</t>
+          <t>553597</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500125</t>
+          <t>582466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>494685</t>
+          <t>509895</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>476579</t>
+          <t>490386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>519626</t>
+          <t>524079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>982080</t>
+          <t>1078504</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>959893</t>
+          <t>1053860</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1005423</t>
+          <t>1098092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,27%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97825</t>
+          <t>103886</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44387</t>
+          <t>85435</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144973</t>
+          <t>125041</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>173392</t>
+          <t>187024</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148112</t>
+          <t>168298</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>195902</t>
+          <t>206546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>271217</t>
+          <t>290911</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171288</t>
+          <t>262961</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>334652</t>
+          <t>318333</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>789961</t>
+          <t>596731</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>742813</t>
+          <t>575576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>843399</t>
+          <t>615182</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>539489</t>
+          <t>549862</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>516979</t>
+          <t>530340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>564769</t>
+          <t>568588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1329450</t>
+          <t>1146593</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1266015</t>
+          <t>1119171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1429379</t>
+          <t>1174543</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>117108</t>
+          <t>123685</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99651</t>
+          <t>105480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136002</t>
+          <t>145150</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>182259</t>
+          <t>200521</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>165245</t>
+          <t>182953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>198252</t>
+          <t>218975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>299367</t>
+          <t>324206</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>274485</t>
+          <t>298568</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>324144</t>
+          <t>354449</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>444126</t>
+          <t>485661</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>425232</t>
+          <t>464196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>461583</t>
+          <t>503866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>365646</t>
+          <t>408334</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>349653</t>
+          <t>389880</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>382660</t>
+          <t>425902</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>809772</t>
+          <t>893996</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>784995</t>
+          <t>863753</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>834654</t>
+          <t>919634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,49%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>75576</t>
+          <t>81378</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65023</t>
+          <t>68680</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88362</t>
+          <t>95729</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>143235</t>
+          <t>157730</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62311</t>
+          <t>143624</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>222748</t>
+          <t>172982</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>218811</t>
+          <t>239108</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117425</t>
+          <t>219277</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>286226</t>
+          <t>260887</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>292589</t>
+          <t>325702</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279803</t>
+          <t>311351</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>303142</t>
+          <t>338400</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>465133</t>
+          <t>281436</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>385620</t>
+          <t>266184</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>546057</t>
+          <t>295542</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>757722</t>
+          <t>607138</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>690307</t>
+          <t>585359</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>859108</t>
+          <t>626969</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>74,09%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>93101</t>
+          <t>102059</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80879</t>
+          <t>87997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105210</t>
+          <t>116596</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>236516</t>
+          <t>259412</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>219724</t>
+          <t>241982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>251309</t>
+          <t>273990</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>361471</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>309740</t>
+          <t>338708</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>347941</t>
+          <t>380644</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>189658</t>
+          <t>208139</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177549</t>
+          <t>193602</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>201880</t>
+          <t>222201</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>189315</t>
+          <t>205197</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>174522</t>
+          <t>190619</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>206107</t>
+          <t>222627</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>378973</t>
+          <t>413336</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>360649</t>
+          <t>394163</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>398850</t>
+          <t>436099</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,28%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>462580</t>
+          <t>496338</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>364903</t>
+          <t>457883</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>519297</t>
+          <t>543216</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>949546</t>
+          <t>1050237</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>764091</t>
+          <t>1006147</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1028185</t>
+          <t>1101531</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1412125</t>
+          <t>1546575</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1213709</t>
+          <t>1477371</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1516243</t>
+          <t>1607726</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2997237</t>
+          <t>3036424</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2940520</t>
+          <t>2989546</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3094914</t>
+          <t>3074879</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2762734</t>
+          <t>2686717</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2684095</t>
+          <t>2635423</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2948189</t>
+          <t>2730807</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5759972</t>
+          <t>5723141</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5655854</t>
+          <t>5661990</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5958388</t>
+          <t>5792345</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
